--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -1959,7 +1959,7 @@
         <v>136782234</v>
       </c>
       <c r="B13" t="n">
-        <v>92734</v>
+        <v>92736</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -10457,7 +10457,7 @@
         <v>136782356</v>
       </c>
       <c r="B86" t="n">
-        <v>91465</v>
+        <v>91467</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -1959,7 +1959,7 @@
         <v>136782234</v>
       </c>
       <c r="B13" t="n">
-        <v>92736</v>
+        <v>92738</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>136962916</v>
       </c>
       <c r="B74" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>137002082</v>
       </c>
       <c r="B75" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10705,7 +10705,7 @@
         <v>136782356</v>
       </c>
       <c r="B88" t="n">
-        <v>91467</v>
+        <v>91469</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11997,7 +11997,7 @@
         <v>136965188</v>
       </c>
       <c r="B99" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -1959,7 +1959,7 @@
         <v>136782234</v>
       </c>
       <c r="B13" t="n">
-        <v>92738</v>
+        <v>92740</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>136962916</v>
       </c>
       <c r="B74" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>137002082</v>
       </c>
       <c r="B75" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10705,7 +10705,7 @@
         <v>136782356</v>
       </c>
       <c r="B88" t="n">
-        <v>91469</v>
+        <v>91471</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11997,7 +11997,7 @@
         <v>136965188</v>
       </c>
       <c r="B99" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -1959,7 +1959,7 @@
         <v>136782234</v>
       </c>
       <c r="B13" t="n">
-        <v>92740</v>
+        <v>92741</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>136962916</v>
       </c>
       <c r="B74" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>137002082</v>
       </c>
       <c r="B75" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10705,7 +10705,7 @@
         <v>136782356</v>
       </c>
       <c r="B88" t="n">
-        <v>91471</v>
+        <v>91472</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11997,7 +11997,7 @@
         <v>136965188</v>
       </c>
       <c r="B99" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -1959,7 +1959,7 @@
         <v>136782234</v>
       </c>
       <c r="B13" t="n">
-        <v>92741</v>
+        <v>92747</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>136962916</v>
       </c>
       <c r="B74" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>137002082</v>
       </c>
       <c r="B75" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10705,7 +10705,7 @@
         <v>136782356</v>
       </c>
       <c r="B88" t="n">
-        <v>91472</v>
+        <v>91478</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11997,7 +11997,7 @@
         <v>136965188</v>
       </c>
       <c r="B99" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -1959,7 +1959,7 @@
         <v>136782234</v>
       </c>
       <c r="B13" t="n">
-        <v>92747</v>
+        <v>92751</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>136962916</v>
       </c>
       <c r="B74" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>137002082</v>
       </c>
       <c r="B75" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10705,7 +10705,7 @@
         <v>136782356</v>
       </c>
       <c r="B88" t="n">
-        <v>91478</v>
+        <v>91482</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11997,7 +11997,7 @@
         <v>136965188</v>
       </c>
       <c r="B99" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -1959,7 +1959,7 @@
         <v>136782234</v>
       </c>
       <c r="B13" t="n">
-        <v>92751</v>
+        <v>92753</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>136962916</v>
       </c>
       <c r="B74" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>137002082</v>
       </c>
       <c r="B75" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10705,7 +10705,7 @@
         <v>136782356</v>
       </c>
       <c r="B88" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11997,7 +11997,7 @@
         <v>136965188</v>
       </c>
       <c r="B99" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -1959,7 +1959,7 @@
         <v>136782234</v>
       </c>
       <c r="B13" t="n">
-        <v>92753</v>
+        <v>92766</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>136962916</v>
       </c>
       <c r="B74" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>137002082</v>
       </c>
       <c r="B75" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10705,7 +10705,7 @@
         <v>136782356</v>
       </c>
       <c r="B88" t="n">
-        <v>91484</v>
+        <v>91497</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11997,7 +11997,7 @@
         <v>136965188</v>
       </c>
       <c r="B99" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12123,7 +12123,7 @@
         <v>136962816</v>
       </c>
       <c r="B100" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12618,7 +12618,7 @@
         <v>136980102</v>
       </c>
       <c r="B104" t="n">
-        <v>56887</v>
+        <v>56900</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>136980097</v>
       </c>
       <c r="B105" t="n">
-        <v>56866</v>
+        <v>56879</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -1959,7 +1959,7 @@
         <v>136782234</v>
       </c>
       <c r="B13" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>136962916</v>
       </c>
       <c r="B74" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>137002082</v>
       </c>
       <c r="B75" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10705,7 +10705,7 @@
         <v>136782356</v>
       </c>
       <c r="B88" t="n">
-        <v>91497</v>
+        <v>91499</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11997,7 +11997,7 @@
         <v>136965188</v>
       </c>
       <c r="B99" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12123,7 +12123,7 @@
         <v>136962816</v>
       </c>
       <c r="B100" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
         <v>136963415</v>
       </c>
       <c r="B103" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12618,7 +12618,7 @@
         <v>136980102</v>
       </c>
       <c r="B104" t="n">
-        <v>56900</v>
+        <v>56902</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>136980097</v>
       </c>
       <c r="B105" t="n">
-        <v>56879</v>
+        <v>56881</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -12151,11 +12151,7 @@
       <c r="I100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
@@ -12516,11 +12512,7 @@
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -12647,11 +12639,7 @@
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>aktiv</t>
-        </is>
-      </c>
+      <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr">
         <is>
           <t>autobox med höghastighetsinspelning</t>
@@ -12778,11 +12766,7 @@
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>aktiv</t>
-        </is>
-      </c>
+      <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr">
         <is>
           <t>autobox med höghastighetsinspelning</t>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -1959,7 +1959,7 @@
         <v>136782234</v>
       </c>
       <c r="B13" t="n">
-        <v>92768</v>
+        <v>92771</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>136962916</v>
       </c>
       <c r="B74" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>137002082</v>
       </c>
       <c r="B75" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10705,7 +10705,7 @@
         <v>136782356</v>
       </c>
       <c r="B88" t="n">
-        <v>91499</v>
+        <v>91502</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11997,7 +11997,7 @@
         <v>136965188</v>
       </c>
       <c r="B99" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -1959,7 +1959,7 @@
         <v>136782234</v>
       </c>
       <c r="B13" t="n">
-        <v>92781</v>
+        <v>92782</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>136962916</v>
       </c>
       <c r="B74" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>137002082</v>
       </c>
       <c r="B75" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9326,7 +9326,7 @@
         <v>137298474</v>
       </c>
       <c r="B76" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10496,7 +10496,7 @@
         <v>137299592</v>
       </c>
       <c r="B86" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10961,7 +10961,7 @@
         <v>136782356</v>
       </c>
       <c r="B90" t="n">
-        <v>91512</v>
+        <v>91513</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>136965188</v>
       </c>
       <c r="B101" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -1959,7 +1959,7 @@
         <v>136782234</v>
       </c>
       <c r="B13" t="n">
-        <v>92782</v>
+        <v>92785</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>136962916</v>
       </c>
       <c r="B74" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>137002082</v>
       </c>
       <c r="B75" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9326,7 +9326,7 @@
         <v>137298474</v>
       </c>
       <c r="B76" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10496,7 +10496,7 @@
         <v>137299592</v>
       </c>
       <c r="B86" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10961,7 +10961,7 @@
         <v>136782356</v>
       </c>
       <c r="B90" t="n">
-        <v>91513</v>
+        <v>91516</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>136965188</v>
       </c>
       <c r="B101" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12379,7 +12379,7 @@
         <v>136962816</v>
       </c>
       <c r="B102" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>137299854</v>
       </c>
       <c r="B103" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12984,7 +12984,7 @@
         <v>136980102</v>
       </c>
       <c r="B107" t="n">
-        <v>56912</v>
+        <v>56913</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13115,7 +13115,7 @@
         <v>136980097</v>
       </c>
       <c r="B108" t="n">
-        <v>56891</v>
+        <v>56892</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -1959,7 +1959,7 @@
         <v>136782234</v>
       </c>
       <c r="B13" t="n">
-        <v>92785</v>
+        <v>92787</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>136962916</v>
       </c>
       <c r="B74" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>137002082</v>
       </c>
       <c r="B75" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9326,7 +9326,7 @@
         <v>137298474</v>
       </c>
       <c r="B76" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10496,7 +10496,7 @@
         <v>137299592</v>
       </c>
       <c r="B86" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10961,7 +10961,7 @@
         <v>136782356</v>
       </c>
       <c r="B90" t="n">
-        <v>91516</v>
+        <v>91518</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>136965188</v>
       </c>
       <c r="B101" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -1959,7 +1959,7 @@
         <v>136782234</v>
       </c>
       <c r="B13" t="n">
-        <v>92787</v>
+        <v>92792</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>136962916</v>
       </c>
       <c r="B74" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>137002082</v>
       </c>
       <c r="B75" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9326,7 +9326,7 @@
         <v>137298474</v>
       </c>
       <c r="B76" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10496,7 +10496,7 @@
         <v>137299592</v>
       </c>
       <c r="B86" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10961,7 +10961,7 @@
         <v>136782356</v>
       </c>
       <c r="B90" t="n">
-        <v>91518</v>
+        <v>91523</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>136965188</v>
       </c>
       <c r="B101" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12379,7 +12379,7 @@
         <v>136962816</v>
       </c>
       <c r="B102" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>137299854</v>
       </c>
       <c r="B103" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -9078,7 +9078,7 @@
         <v>136962916</v>
       </c>
       <c r="B74" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>137002082</v>
       </c>
       <c r="B75" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9326,7 +9326,7 @@
         <v>137298474</v>
       </c>
       <c r="B76" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10496,7 +10496,7 @@
         <v>137299592</v>
       </c>
       <c r="B86" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>136965188</v>
       </c>
       <c r="B101" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -9078,7 +9078,7 @@
         <v>136962916</v>
       </c>
       <c r="B74" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>137002082</v>
       </c>
       <c r="B75" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9326,7 +9326,7 @@
         <v>137298474</v>
       </c>
       <c r="B76" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10496,7 +10496,7 @@
         <v>137299592</v>
       </c>
       <c r="B86" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>136965188</v>
       </c>
       <c r="B101" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -9078,7 +9078,7 @@
         <v>136962916</v>
       </c>
       <c r="B74" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>137002082</v>
       </c>
       <c r="B75" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9326,7 +9326,7 @@
         <v>137298474</v>
       </c>
       <c r="B76" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10496,7 +10496,7 @@
         <v>137299592</v>
       </c>
       <c r="B86" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>136965188</v>
       </c>
       <c r="B101" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -9078,7 +9078,7 @@
         <v>136962916</v>
       </c>
       <c r="B74" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>137002082</v>
       </c>
       <c r="B75" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>136965188</v>
       </c>
       <c r="B101" t="n">
-        <v>93523</v>
+        <v>93524</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 4086-2025 artfynd.xlsx
+++ b/artfynd/A 4086-2025 artfynd.xlsx
@@ -9078,7 +9078,7 @@
         <v>136962916</v>
       </c>
       <c r="B74" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>137002082</v>
       </c>
       <c r="B75" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9326,7 +9326,7 @@
         <v>137298474</v>
       </c>
       <c r="B76" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10496,7 +10496,7 @@
         <v>137299592</v>
       </c>
       <c r="B86" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>136965188</v>
       </c>
       <c r="B101" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12379,7 +12379,7 @@
         <v>136962816</v>
       </c>
       <c r="B102" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>137299854</v>
       </c>
       <c r="B103" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12984,7 +12984,7 @@
         <v>136980102</v>
       </c>
       <c r="B107" t="n">
-        <v>56913</v>
+        <v>56916</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13115,7 +13115,7 @@
         <v>136980097</v>
       </c>
       <c r="B108" t="n">
-        <v>56892</v>
+        <v>56895</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
